--- a/output/Python/gpt-5-2025-08-07/task_analysis_results_singlepass_Python_gpt-5-2025-08-07_zebralogic.xlsx
+++ b/output/Python/gpt-5-2025-08-07/task_analysis_results_singlepass_Python_gpt-5-2025-08-07_zebralogic.xlsx
@@ -1452,7 +1452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1502,26 +1502,69 @@
         <v>1</v>
       </c>
       <c r="C2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Hobby",
+      "Height",
+      "Food"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "knitting",
+        "short",
+        "spaghetti"
+      ],
+      [
+        "2",
+        "Eric",
+        "painting",
+        "very tall",
+        "stew"
+      ],
+      [
+        "3",
+        "Bob",
+        "photography",
+        "tall",
+        "grilled cheese"
+      ],
+      [
+        "4",
+        "Alice",
+        "cooking",
+        "average",
+        "stir fry"
+      ],
+      [
+        "5",
+        "Arnold",
+        "gardening",
+        "very short",
+        "pizza"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -1580,10 +1623,12 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 21:56:35.py", line 279, in &lt;module&gt;
+    result = solve_puzzle()
+             ^^^^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 21:56:35.py", line 251, in solve_puzzle
+    raise ValueError(f"Duplicate assignment in category {cat} for house {h}")
+ValueError: Duplicate assignment in category PhoneModel for house 5</t>
         </is>
       </c>
     </row>
@@ -1597,26 +1642,22 @@
         <v>1</v>
       </c>
       <c r="C5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Flower", "HairColor", "FavoriteSport", "HouseStyle", "Pet"], "rows": [["1", "Arnold", "carnations", "brown", "tennis", "victorian", "fish"], ["2", "Peter", "daffodils", "blonde", "basketball", "ranch", "dog"], ["3", "Eric", "lilies", "black", "soccer", "colonial", "cat"]]}}</t>
         </is>
       </c>
     </row>
@@ -1630,26 +1671,69 @@
         <v>1</v>
       </c>
       <c r="C6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Children",
+      "Smoothie"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "Bella",
+        "blueberry"
+      ],
+      [
+        "2",
+        "Carol",
+        "Fred",
+        "cherry"
+      ],
+      [
+        "3",
+        "Eric",
+        "Samantha",
+        "desert"
+      ],
+      [
+        "4",
+        "Alice",
+        "Alice",
+        "watermelon"
+      ],
+      [
+        "5",
+        "Bob",
+        "Timothy",
+        "lime"
+      ],
+      [
+        "6",
+        "Peter",
+        "Meredith",
+        "dragonfruit"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -1663,26 +1747,51 @@
         <v>1</v>
       </c>
       <c r="C7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve_puzzle()
-    ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Hobby",
+      "BookGenre",
+      "MusicGenre",
+      "Birthday"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "gardening",
+        "mystery",
+        "rock",
+        "sept"
+      ],
+      [
+        "2",
+        "Arnold",
+        "photography",
+        "science fiction",
+        "pop",
+        "april"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -1696,26 +1805,22 @@
         <v>1</v>
       </c>
       <c r="C8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Flower", "Height", "Mother", "Occupation", "FavoriteSport"], "rows": [["1", "Arnold", "lilies", "tall", "Kailyn", "teacher", "tennis"], ["2", "Peter", "carnations", "average", "Janelle", "doctor", "basketball"], ["3", "Eric", "roses", "very short", "Holly", "engineer", "swimming"], ["4", "Alice", "daffodils", "short", "Aniya", "artist", "soccer"]]}}</t>
         </is>
       </c>
     </row>
@@ -1729,26 +1834,22 @@
         <v>1</v>
       </c>
       <c r="C9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    print(json.dumps(solve_puzzle(), ensure_ascii=False))
-          ^^^^
-NameError: name 'json' is not defined. Did you forget to import 'json'?</t>
+          <t>{"solution": {"header": ["House", "Name", "Height"], "rows": [["1", "Eric", "short"], ["2", "Arnold", "average"], ["3", "Peter", "very short"]]}}</t>
         </is>
       </c>
     </row>
@@ -1778,10 +1879,12 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 21:56:35.py", line 279, in &lt;module&gt;
+    solve()
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 21:56:35.py", line 192, in solve
+    if house_of(pet_map, "hamster") &lt;= house_of(month_map, "mar"):
+       ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+TypeError: '&lt;=' not supported between instances of 'NoneType' and 'int'</t>
         </is>
       </c>
     </row>
@@ -1795,26 +1898,22 @@
         <v>1</v>
       </c>
       <c r="C11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Height"], "rows": [["1", "Eric", "very tall"], ["2", "Peter", "short"], ["3", "Bob", "very short"], ["4", "Alice", "tall"], ["5", "Arnold", "average"]]}}</t>
         </is>
       </c>
     </row>
@@ -1828,26 +1927,22 @@
         <v>1</v>
       </c>
       <c r="C12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Flower", "Animal"], "rows": [["1", "Arnold", "lilies", "bird"], ["2", "Alice", "carnations", "dog"], ["3", "Eric", "tulips", "horse"], ["4", "Peter", "daffodils", "fish"], ["5", "Bob", "roses", "cat"]]}}</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1971,66 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "Vacation", "Education", "Color", "PhoneModel", "Food"], "rows": [["1", "Peter", "camping", "high school", "white", "iphone 13", "spaghetti"], ["2", "Bob", "mountain", "bachelor", "blue", "huawei p50", "stir fry"], ["3", "Eric", "city", "doctorate", "yellow", "samsung galaxy s21", "pizza"], ["4", "Alice", "cruise", "master", "green", "oneplus 9", "stew"], ["5", "Arnold", "beach", "associate", "red", "google pixel 6", "grilled cheese"]]}}</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Vacation",
+      "Education",
+      "Color",
+      "PhoneModel",
+      "Food"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "camping",
+        "high school",
+        "white",
+        "iphone 13",
+        "spaghetti"
+      ],
+      [
+        "2",
+        "Bob",
+        "mountain",
+        "bachelor",
+        "blue",
+        "huawei p50",
+        "stir fry"
+      ],
+      [
+        "3",
+        "Eric",
+        "city",
+        "doctorate",
+        "yellow",
+        "samsung galaxy s21",
+        "pizza"
+      ],
+      [
+        "4",
+        "Alice",
+        "cruise",
+        "master",
+        "green",
+        "oneplus 9",
+        "stew"
+      ],
+      [
+        "5",
+        "Arnold",
+        "beach",
+        "associate",
+        "red",
+        "google pixel 6",
+        "grilled cheese"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -1890,26 +2044,22 @@
         <v>1</v>
       </c>
       <c r="C14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Smoothie", "Cigar", "Height", "PhoneModel"], "rows": [["1", "Eric", "dragonfruit", "pall mall", "average", "samsung galaxy s21"], ["2", "Peter", "desert", "blue master", "very short", "iphone 13"], ["3", "Alice", "watermelon", "prince", "tall", "oneplus 9"], ["4", "Arnold", "cherry", "dunhill", "short", "google pixel 6"]]}}</t>
         </is>
       </c>
     </row>
@@ -1923,26 +2073,22 @@
         <v>1</v>
       </c>
       <c r="C15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle"], "rows": [["1", "Eric", "ranch"], ["2", "Alice", "craftsman"], ["3", "Arnold", "victorian"], ["4", "Peter", "colonial"]]}}</t>
         </is>
       </c>
     </row>
@@ -1956,26 +2102,22 @@
         <v>1</v>
       </c>
       <c r="C16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "BookGenre", "Vacation"], "rows": [["1", "Eric", "mystery", "mountain"], ["2", "Arnold", "science fiction", "beach"], ["3", "Peter", "romance", "city"]]}}</t>
         </is>
       </c>
     </row>
@@ -1989,26 +2131,22 @@
         <v>1</v>
       </c>
       <c r="C17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Animal", "Occupation", "FavoriteSport", "Height"], "rows": [["1", "Peter", "bird", "nurse", "baseball", "very tall"], ["2", "Eric", "dog", "engineer", "swimming", "average"], ["3", "Alice", "rabbit", "artist", "volleyball", "tall"], ["4", "Bob", "horse", "teacher", "tennis", "very short"], ["5", "Carol", "fish", "lawyer", "soccer", "super tall"], ["6", "Arnold", "cat", "doctor", "basketball", "short"]]}}</t>
         </is>
       </c>
     </row>
@@ -2022,26 +2160,75 @@
         <v>1</v>
       </c>
       <c r="C18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Birthday",
+      "Mother",
+      "Occupation",
+      "HairColor"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "feb",
+        "Penny",
+        "doctor",
+        "red"
+      ],
+      [
+        "2",
+        "Peter",
+        "sept",
+        "Holly",
+        "lawyer",
+        "black"
+      ],
+      [
+        "3",
+        "Arnold",
+        "april",
+        "Janelle",
+        "engineer",
+        "blonde"
+      ],
+      [
+        "4",
+        "Bob",
+        "jan",
+        "Aniya",
+        "artist",
+        "brown"
+      ],
+      [
+        "5",
+        "Alice",
+        "mar",
+        "Kailyn",
+        "teacher",
+        "gray"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2055,26 +2242,22 @@
         <v>1</v>
       </c>
       <c r="C19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Height"], "rows": [["1", "Peter", "average"], ["2", "Eric", "very short"], ["3", "Arnold", "short"]]}}</t>
         </is>
       </c>
     </row>
@@ -2088,26 +2271,63 @@
         <v>1</v>
       </c>
       <c r="C20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Mother",
+      "Height"
+    ],
+    "rows": [
+      [
+        "1",
+        "Bob",
+        "Janelle",
+        "tall"
+      ],
+      [
+        "2",
+        "Eric",
+        "Kailyn",
+        "average"
+      ],
+      [
+        "3",
+        "Peter",
+        "Holly",
+        "short"
+      ],
+      [
+        "4",
+        "Arnold",
+        "Penny",
+        "very tall"
+      ],
+      [
+        "5",
+        "Alice",
+        "Aniya",
+        "very short"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2121,26 +2341,52 @@
         <v>1</v>
       </c>
       <c r="C21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Pet"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "fish"
+      ],
+      [
+        "2",
+        "Alice",
+        "cat"
+      ],
+      [
+        "3",
+        "Peter",
+        "dog"
+      ],
+      [
+        "4",
+        "Eric",
+        "bird"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2154,26 +2400,22 @@
         <v>1</v>
       </c>
       <c r="C22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "HairColor"], "rows": [["1", "Alice", "red"], ["2", "Arnold", "black"], ["3", "Eric", "brown"], ["4", "Peter", "blonde"]]}}</t>
         </is>
       </c>
     </row>
@@ -2187,26 +2429,63 @@
         <v>1</v>
       </c>
       <c r="C23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    res = solve()
-          ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Animal",
+      "Birthday",
+      "Hobby",
+      "Drink",
+      "HairColor"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "horse",
+        "jan",
+        "photography",
+        "water",
+        "blonde"
+      ],
+      [
+        "2",
+        "Eric",
+        "cat",
+        "sept",
+        "cooking",
+        "tea",
+        "brown"
+      ],
+      [
+        "3",
+        "Arnold",
+        "bird",
+        "april",
+        "gardening",
+        "milk",
+        "black"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2220,26 +2499,22 @@
         <v>1</v>
       </c>
       <c r="C24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Drink", "Vacation", "HouseStyle", "Animal", "Birthday"], "rows": [["1", "Arnold", "tea", "beach", "colonial", "bird", "sept"], ["2", "Peter", "milk", "city", "ranch", "horse", "jan"], ["3", "Eric", "water", "mountain", "victorian", "cat", "april"]]}}</t>
         </is>
       </c>
     </row>
@@ -2253,26 +2528,22 @@
         <v>1</v>
       </c>
       <c r="C25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Drink", "Nationality", "Education", "HouseStyle", "Smoothie"], "rows": [["1", "Eric", "milk", "dane", "high school", "ranch", "watermelon"], ["2", "Peter", "water", "swede", "bachelor", "victorian", "desert"], ["3", "Arnold", "tea", "brit", "associate", "colonial", "cherry"]]}}</t>
         </is>
       </c>
     </row>
@@ -2286,26 +2557,22 @@
         <v>1</v>
       </c>
       <c r="C26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "BookGenre", "Occupation"], "rows": [["1", "Carol", "mystery", "doctor"], ["2", "Bob", "science fiction", "artist"], ["3", "Eric", "historical fiction", "nurse"], ["4", "Alice", "fantasy", "lawyer"], ["5", "Arnold", "biography", "teacher"], ["6", "Peter", "romance", "engineer"]]}}</t>
         </is>
       </c>
     </row>
@@ -2319,26 +2586,63 @@
         <v>1</v>
       </c>
       <c r="C27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "CarModel",
+      "HouseStyle",
+      "Pet",
+      "Occupation",
+      "Vacation"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "tesla model 3",
+        "ranch",
+        "fish",
+        "doctor",
+        "city"
+      ],
+      [
+        "2",
+        "Peter",
+        "toyota camry",
+        "victorian",
+        "dog",
+        "engineer",
+        "beach"
+      ],
+      [
+        "3",
+        "Arnold",
+        "ford f150",
+        "colonial",
+        "cat",
+        "teacher",
+        "mountain"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2352,26 +2656,22 @@
         <v>1</v>
       </c>
       <c r="C28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Vacation", "Height", "Flower", "HairColor", "Education"], "rows": [["1", "Eric", "beach", "very short", "lilies", "brown", "bachelor"], ["2", "Peter", "mountain", "average", "carnations", "black", "associate"], ["3", "Arnold", "city", "short", "daffodils", "blonde", "high school"]]}}</t>
         </is>
       </c>
     </row>
@@ -2401,10 +2701,13 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    print(json.dumps(solve_puzzle(), ensure_ascii=False))
-          ^^^^
-NameError: name 'json' is not defined. Did you forget to import 'json'?</t>
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 57, in &lt;module&gt;
+    solution = solve_puzzle()
+               ^^^^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 30, in solve_puzzle
+    if edu_arr[pos(name_arr.index("Peter"))] != "high school":
+               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+TypeError: solve_puzzle.&lt;locals&gt;.pos() missing 1 required positional argument: 'value'</t>
         </is>
       </c>
     </row>
@@ -2418,26 +2721,81 @@
         <v>1</v>
       </c>
       <c r="C30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "HouseStyle",
+      "Mother",
+      "PhoneModel",
+      "Drink",
+      "Animal"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "victorian",
+        "Aniya",
+        "huawei p50",
+        "root beer",
+        "cat"
+      ],
+      [
+        "2",
+        "Arnold",
+        "ranch",
+        "Kailyn",
+        "iphone 13",
+        "milk",
+        "dog"
+      ],
+      [
+        "3",
+        "Eric",
+        "modern",
+        "Penny",
+        "oneplus 9",
+        "coffee",
+        "horse"
+      ],
+      [
+        "4",
+        "Bob",
+        "craftsman",
+        "Holly",
+        "google pixel 6",
+        "tea",
+        "bird"
+      ],
+      [
+        "5",
+        "Alice",
+        "colonial",
+        "Janelle",
+        "samsung galaxy s21",
+        "water",
+        "fish"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2451,26 +2809,76 @@
         <v>1</v>
       </c>
       <c r="C31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "HouseStyle",
+      "MusicGenre",
+      "Hobby"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "craftsman",
+        "country",
+        "painting"
+      ],
+      [
+        "2",
+        "Carol",
+        "mediterranean",
+        "hip hop",
+        "cooking"
+      ],
+      [
+        "3",
+        "Bob",
+        "colonial",
+        "classical",
+        "knitting"
+      ],
+      [
+        "4",
+        "Peter",
+        "victorian",
+        "jazz",
+        "woodworking"
+      ],
+      [
+        "5",
+        "Eric",
+        "ranch",
+        "rock",
+        "gardening"
+      ],
+      [
+        "6",
+        "Alice",
+        "modern",
+        "pop",
+        "photography"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2484,26 +2892,54 @@
         <v>1</v>
       </c>
       <c r="C32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Occupation",
+      "Birthday",
+      "HouseStyle",
+      "Height",
+      "Cigar"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "engineer",
+        "april",
+        "colonial",
+        "very short",
+        "prince"
+      ],
+      [
+        "2",
+        "Arnold",
+        "doctor",
+        "sept",
+        "victorian",
+        "short",
+        "pall mall"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2517,26 +2953,22 @@
         <v>1</v>
       </c>
       <c r="C33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Education", "Height", "Food", "Drink"], "rows": [["1", "Arnold", "high school", "very short", "pizza", "water"], ["2", "Eric", "associate", "short", "grilled cheese", "tea"]]}}</t>
         </is>
       </c>
     </row>
@@ -2550,26 +2982,22 @@
         <v>1</v>
       </c>
       <c r="C34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    print(json.dumps(solve_puzzle(), ensure_ascii=False))
-          ^^^^
-NameError: name 'json' is not defined. Did you forget to import 'json'?</t>
+          <t>{"solution": {"header": ["House", "Name", "Hobby", "Pet", "Height"], "rows": [["1", "Eric", "photography", "dog", "very short"], ["2", "Arnold", "gardening", "cat", "short"]]}}</t>
         </is>
       </c>
     </row>
@@ -2583,26 +3011,22 @@
         <v>1</v>
       </c>
       <c r="C35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    print(json.dumps(solve_puzzle(), ensure_ascii=False))
-          ^^^^
-NameError: name 'json' is not defined. Did you forget to import 'json'?</t>
+          <t>{"solution": {"header": ["House", "Name", "Smoothie", "Flower", "Animal", "Hobby"], "rows": [["1", "Arnold", "desert", "daffodils", "cat", "cooking"], ["2", "Peter", "watermelon", "carnations", "horse", "gardening"], ["3", "Eric", "cherry", "lilies", "bird", "photography"]]}}</t>
         </is>
       </c>
     </row>
@@ -2616,26 +3040,22 @@
         <v>1</v>
       </c>
       <c r="C36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "HairColor", "FavoriteSport", "Smoothie"], "rows": [["1", "Arnold", "brown", "basketball", "desert"], ["2", "Eric", "black", "soccer", "cherry"]]}}</t>
         </is>
       </c>
     </row>
@@ -2649,26 +3069,52 @@
         <v>1</v>
       </c>
       <c r="C37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Color"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "white"
+      ],
+      [
+        "2",
+        "Alice",
+        "red"
+      ],
+      [
+        "3",
+        "Arnold",
+        "green"
+      ],
+      [
+        "4",
+        "Eric",
+        "yellow"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2682,26 +3128,22 @@
         <v>1</v>
       </c>
       <c r="C38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "MusicGenre"], "rows": [["1", "Peter", "pop"], ["2", "Eric", "rock"], ["3", "Bob", "hip hop"], ["4", "Arnold", "jazz"], ["5", "Alice", "classical"], ["6", "Carol", "country"]]}}</t>
         </is>
       </c>
     </row>
@@ -2715,26 +3157,22 @@
         <v>1</v>
       </c>
       <c r="C39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "HairColor", "MusicGenre"], "rows": [["1", "Alice", "black", "classical"], ["2", "Arnold", "blonde", "rock"], ["3", "Eric", "red", "jazz"], ["4", "Peter", "brown", "pop"]]}}</t>
         </is>
       </c>
     </row>
@@ -2748,26 +3186,55 @@
         <v>1</v>
       </c>
       <c r="C40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve_puzzle()
-    ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "MusicGenre",
+      "Children",
+      "BookGenre"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "pop",
+        "Fred",
+        "romance"
+      ],
+      [
+        "2",
+        "Eric",
+        "classical",
+        "Bella",
+        "mystery"
+      ],
+      [
+        "3",
+        "Arnold",
+        "rock",
+        "Meredith",
+        "science fiction"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2781,26 +3248,75 @@
         <v>1</v>
       </c>
       <c r="C41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Nationality",
+      "Vacation",
+      "Education",
+      "Occupation"
+    ],
+    "rows": [
+      [
+        "1",
+        "Alice",
+        "german",
+        "beach",
+        "doctorate",
+        "doctor"
+      ],
+      [
+        "2",
+        "Arnold",
+        "norwegian",
+        "cruise",
+        "associate",
+        "lawyer"
+      ],
+      [
+        "3",
+        "Bob",
+        "dane",
+        "city",
+        "bachelor",
+        "engineer"
+      ],
+      [
+        "4",
+        "Eric",
+        "brit",
+        "camping",
+        "master",
+        "teacher"
+      ],
+      [
+        "5",
+        "Peter",
+        "swede",
+        "mountain",
+        "high school",
+        "artist"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2843,26 +3359,22 @@
         <v>1</v>
       </c>
       <c r="C43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    main()
-    ^^^^
-NameError: name 'main' is not defined. Did you mean: 'min'?</t>
+          <t>{"solution": {"header": ["House", "Name", "Occupation", "Education", "Smoothie", "Hobby"], "rows": [["1", "Arnold", "engineer", "high school", "watermelon", "gardening"], ["2", "Peter", "doctor", "associate", "desert", "cooking"], ["3", "Eric", "teacher", "bachelor", "cherry", "photography"]]}}</t>
         </is>
       </c>
     </row>
@@ -2876,26 +3388,22 @@
         <v>1</v>
       </c>
       <c r="C44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Hobby", "Birthday", "Education", "Smoothie"], "rows": [["1", "Arnold", "photography", "april", "associate", "dragonfruit"], ["2", "Eric", "gardening", "jan", "bachelor", "desert"], ["3", "Alice", "cooking", "sept", "high school", "cherry"], ["4", "Peter", "painting", "feb", "master", "watermelon"]]}}</t>
         </is>
       </c>
     </row>
@@ -2924,11 +3432,23 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    main()
-    ^^^^
-NameError: name 'main' is not defined. Did you mean: 'min'?</t>
+          <t xml:space="preserve">Traceback (most recent call last):
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 465, in &lt;module&gt;
+    result = solve_puzzle()
+             ^^^^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 447, in solve_puzzle
+    solved = backtrack()
+             ^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 429, in backtrack
+    if backtrack():
+       ^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 429, in backtrack
+    if backtrack():
+       ^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 429, in backtrack
+    if backtrack():
+       ^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 422, in </t>
         </is>
       </c>
     </row>
@@ -2942,26 +3462,72 @@
         <v>1</v>
       </c>
       <c r="C46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Flower",
+      "Hobby",
+      "Pet",
+      "Color",
+      "HouseStyle"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "daffodils",
+        "gardening",
+        "bird",
+        "yellow",
+        "ranch"
+      ],
+      [
+        "2",
+        "Arnold",
+        "carnations",
+        "painting",
+        "fish",
+        "white",
+        "craftsman"
+      ],
+      [
+        "3",
+        "Alice",
+        "roses",
+        "photography",
+        "dog",
+        "red",
+        "colonial"
+      ],
+      [
+        "4",
+        "Eric",
+        "lilies",
+        "cooking",
+        "cat",
+        "green",
+        "victorian"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -2975,11 +3541,11 @@
         <v>1</v>
       </c>
       <c r="C47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Wrong plan</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -2990,11 +3556,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    main()
-    ^^^^
-NameError: name 'main' is not defined. Did you mean: 'min'?</t>
+          <t>{"solution": {"header": ["House", "Name", "Food", "CarModel", "PhoneModel", "Occupation", "Drink"], "rows": [["1", "Alice", "stir fry", "bmw 3 series", "samsung galaxy s21", "engineer", "water"], ["2", "Arnold", "stew", "honda civic", "google pixel 6", "doctor", "coffee"], ["3", "Bob", "spaghetti", "ford f150", "oneplus 9", "lawyer", "milk"], ["4", "Peter", "grilled cheese", "", "huawei p50", "teacher", ""], ["5", "", "pizza", "", "", "", ""]]}}</t>
         </is>
       </c>
     </row>
@@ -3008,26 +3570,76 @@
         <v>1</v>
       </c>
       <c r="C48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "CarModel",
+      "Mother",
+      "Hobby"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "honda civic",
+        "Janelle",
+        "woodworking"
+      ],
+      [
+        "2",
+        "Eric",
+        "tesla model 3",
+        "Holly",
+        "gardening"
+      ],
+      [
+        "3",
+        "Peter",
+        "chevrolet silverado",
+        "Aniya",
+        "knitting"
+      ],
+      [
+        "4",
+        "Carol",
+        "ford f150",
+        "Sarah",
+        "photography"
+      ],
+      [
+        "5",
+        "Bob",
+        "bmw 3 series",
+        "Penny",
+        "painting"
+      ],
+      [
+        "6",
+        "Alice",
+        "toyota camry",
+        "Kailyn",
+        "cooking"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -3041,26 +3653,69 @@
         <v>1</v>
       </c>
       <c r="C49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    main()
-    ^^^^
-NameError: name 'main' is not defined. Did you mean: 'min'?</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Occupation",
+      "CarModel"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "doctor",
+        "tesla model 3"
+      ],
+      [
+        "2",
+        "Carol",
+        "teacher",
+        "bmw 3 series"
+      ],
+      [
+        "3",
+        "Bob",
+        "engineer",
+        "honda civic"
+      ],
+      [
+        "4",
+        "Peter",
+        "nurse",
+        "toyota camry"
+      ],
+      [
+        "5",
+        "Arnold",
+        "artist",
+        "ford f150"
+      ],
+      [
+        "6",
+        "Alice",
+        "lawyer",
+        "chevrolet silverado"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -3074,26 +3729,22 @@
         <v>1</v>
       </c>
       <c r="C50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solution = solve_puzzle()
-               ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "PhoneModel"], "rows": [["1", "Eric", "huawei p50"], ["2", "Peter", "samsung galaxy s21"], ["3", "Bob", "xiaomi mi 11"], ["4", "Alice", "iphone 13"], ["5", "Carol", "google pixel 6"], ["6", "Arnold", "oneplus 9"]]}}</t>
         </is>
       </c>
     </row>
@@ -3107,26 +3758,22 @@
         <v>1</v>
       </c>
       <c r="C51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    main()
-    ^^^^
-NameError: name 'main' is not defined. Did you mean: 'min'?</t>
+          <t>{"solution": {"header": ["House", "Name", "Height", "Cigar", "Smoothie", "PhoneModel"], "rows": [["1", "Peter", "short", "blends", "watermelon", "samsung galaxy s21"], ["2", "Eric", "very tall", "prince", "desert", "iphone 13"], ["3", "Arnold", "tall", "blue master", "cherry", "oneplus 9"], ["4", "Alice", "very short", "pall mall", "lime", "huawei p50"], ["5", "Bob", "average", "dunhill", "dragonfruit", "google pixel 6"]]}}</t>
         </is>
       </c>
     </row>
@@ -3140,26 +3787,22 @@
         <v>1</v>
       </c>
       <c r="C52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle", "Smoothie", "Pet"], "rows": [["1", "Arnold", "victorian", "cherry", "dog"], ["2", "Eric", "colonial", "desert", "cat"]]}}</t>
         </is>
       </c>
     </row>
@@ -3173,26 +3816,69 @@
         <v>1</v>
       </c>
       <c r="C53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Color",
+      "PhoneModel",
+      "Occupation"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "green",
+        "google pixel 6",
+        "teacher"
+      ],
+      [
+        "2",
+        "Bob",
+        "blue",
+        "samsung galaxy s21",
+        "doctor"
+      ],
+      [
+        "3",
+        "Peter",
+        "red",
+        "huawei p50",
+        "artist"
+      ],
+      [
+        "4",
+        "Alice",
+        "yellow",
+        "oneplus 9",
+        "lawyer"
+      ],
+      [
+        "5",
+        "Arnold",
+        "white",
+        "iphone 13",
+        "engineer"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -3206,231 +3892,373 @@
         <v>1</v>
       </c>
       <c r="C54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    main()
-    ^^^^
-NameError: name 'main' is not defined. Did you mean: 'min'?</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Height",
+      "Mother",
+      "HairColor"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "average",
+        "Aniya",
+        "brown"
+      ],
+      [
+        "2",
+        "Eric",
+        "very short",
+        "Penny",
+        "black"
+      ],
+      [
+        "3",
+        "Alice",
+        "very tall",
+        "Kailyn",
+        "gray"
+      ],
+      [
+        "4",
+        "Peter",
+        "short",
+        "Janelle",
+        "red"
+      ],
+      [
+        "5",
+        "Bob",
+        "tall",
+        "Holly",
+        "blonde"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x4-36</t>
+          <t>zebralogic_example_lgp-test-2x2-5</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>1</v>
       </c>
       <c r="C55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle"], "rows": [["1", "Eric", "victorian"], ["2", "Arnold", "colonial"]]}}</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-5x4-27</t>
+          <t>zebralogic_example_lgp-test-2x4-36</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "BookGenre",
+      "Birthday",
+      "Animal"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "mystery",
+        "sept",
+        "horse"
+      ],
+      [
+        "2",
+        "Arnold",
+        "science fiction",
+        "april",
+        "cat"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-3x3-29</t>
+          <t>zebralogic_example_lgp-test-5x4-27</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Birthday",
+      "Cigar",
+      "Drink"
+    ],
+    "rows": [
+      [
+        "1",
+        "Bob",
+        "april",
+        "prince",
+        "milk"
+      ],
+      [
+        "2",
+        "Alice",
+        "feb",
+        "blends",
+        "tea"
+      ],
+      [
+        "3",
+        "Eric",
+        "jan",
+        "pall mall",
+        "root beer"
+      ],
+      [
+        "4",
+        "Arnold",
+        "sept",
+        "blue master",
+        "coffee"
+      ],
+      [
+        "5",
+        "Peter",
+        "mar",
+        "dunhill",
+        "water"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-4x6-11</t>
+          <t>zebralogic_example_lgp-test-3x3-29</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = zebra_solver()
-             ^^^^^^^^^^^^
-NameError: name 'zebra_solver' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Mother", "Food"], "rows": [["1", "Eric", "Janelle", "grilled cheese"], ["2", "Arnold", "Aniya", "spaghetti"], ["3", "Peter", "Holly", "pizza"]]}}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-3x3-19</t>
+          <t>zebralogic_example_lgp-test-4x6-11</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    print(json.dumps(solve_puzzle(), ensure_ascii=False))
-          ^^^^
-NameError: name 'json' is not defined. Did you forget to import 'json'?</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Hobby",
+      "Animal",
+      "BookGenre",
+      "Birthday",
+      "MusicGenre"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "painting",
+        "fish",
+        "fantasy",
+        "feb",
+        "pop"
+      ],
+      [
+        "2",
+        "Alice",
+        "cooking",
+        "bird",
+        "romance",
+        "sept",
+        "jazz"
+      ],
+      [
+        "3",
+        "Arnold",
+        "gardening",
+        "horse",
+        "mystery",
+        "april",
+        "rock"
+      ],
+      [
+        "4",
+        "Eric",
+        "photography",
+        "cat",
+        "science fiction",
+        "jan",
+        "classical"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-5x3-25</t>
+          <t>zebralogic_example_lgp-test-3x3-19</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Smoothie", "BookGenre"], "rows": [["1", "Peter", "cherry", "romance"], ["2", "Eric", "desert", "science fiction"], ["3", "Arnold", "watermelon", "mystery"]]}}</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-6x2-14</t>
+          <t>zebralogic_example_lgp-test-5x3-25</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3453,578 +4281,782 @@
       <c r="G61" t="inlineStr">
         <is>
           <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve_puzzle()
-    ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 85, in &lt;module&gt;
+    solution = solve_puzzle()
+               ^^^^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 44, in solve_puzzle
+    if heights[heights.index("very short")] &gt;= idx_arnold:
+       ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+TypeError: '&gt;=' not supported between instances of 'str' and 'int'</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-4x5-14</t>
+          <t>zebralogic_example_lgp-test-6x2-14</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Cigar"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "dunhill"
+      ],
+      [
+        "2",
+        "Arnold",
+        "yellow monster"
+      ],
+      [
+        "3",
+        "Bob",
+        "pall mall"
+      ],
+      [
+        "4",
+        "Alice",
+        "blends"
+      ],
+      [
+        "5",
+        "Carol",
+        "blue master"
+      ],
+      [
+        "6",
+        "Eric",
+        "prince"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-5x2-18</t>
+          <t>zebralogic_example_lgp-test-4x5-14</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    res = solve_puzzle()
-          ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Mother",
+      "Smoothie",
+      "Height",
+      "Education"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "Kailyn",
+        "watermelon",
+        "very short",
+        "associate"
+      ],
+      [
+        "2",
+        "Peter",
+        "Aniya",
+        "cherry",
+        "average",
+        "high school"
+      ],
+      [
+        "3",
+        "Alice",
+        "Janelle",
+        "dragonfruit",
+        "tall",
+        "bachelor"
+      ],
+      [
+        "4",
+        "Arnold",
+        "Holly",
+        "desert",
+        "short",
+        "master"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-5x3-22</t>
+          <t>zebralogic_example_lgp-test-5x2-18</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solution = solve()
-               ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Children"], "rows": [["1", "Bob", "Timothy"], ["2", "Alice", "Fred"], ["3", "Arnold", "Bella"], ["4", "Eric", "Samantha"], ["5", "Peter", "Meredith"]]}}</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-4x2-2</t>
+          <t>zebralogic_example_lgp-test-5x3-22</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Smoothie", "Nationality"], "rows": [["1", "Arnold", "lime", "swede"], ["2", "Peter", "dragonfruit", "german"], ["3", "Alice", "watermelon", "norwegian"], ["4", "Bob", "desert", "dane"], ["5", "Eric", "cherry", "brit"]]}}</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-6x5-38</t>
+          <t>zebralogic_example_lgp-test-4x2-2</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "HouseStyle"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "ranch"
+      ],
+      [
+        "2",
+        "Alice",
+        "victorian"
+      ],
+      [
+        "3",
+        "Eric",
+        "craftsman"
+      ],
+      [
+        "4",
+        "Arnold",
+        "colonial"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-6x2-5</t>
+          <t>zebralogic_example_lgp-test-6x5-38</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solution = solve_puzzle()
-               ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Birthday", "Food", "Height", "CarModel"], "rows": [["1", "Alice", "mar", "stir fry", "short", "honda civic"], ["2", "Arnold", "sept", "spaghetti", "average", "bmw 3 series"], ["3", "Peter", "may", "grilled cheese", "super tall", "chevrolet silverado"], ["4", "Carol", "feb", "pizza", "very short", "tesla model 3"], ["5", "Bob", "april", "soup", "tall", "ford f150"], ["6", "Eric", "jan", "stew", "very tall", "toyota camry"]]}}</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-6x3-18</t>
+          <t>zebralogic_example_lgp-test-6x2-5</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    main()
-    ^^^^
-NameError: name 'main' is not defined. Did you mean: 'min'?</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Vacation"
+    ],
+    "rows": [
+      [
+        "1",
+        "Alice",
+        "mountain"
+      ],
+      [
+        "2",
+        "Eric",
+        "camping"
+      ],
+      [
+        "3",
+        "Peter",
+        "cultural"
+      ],
+      [
+        "4",
+        "Carol",
+        "city"
+      ],
+      [
+        "5",
+        "Bob",
+        "cruise"
+      ],
+      [
+        "6",
+        "Arnold",
+        "beach"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-3x5-17</t>
+          <t>zebralogic_example_lgp-test-6x3-18</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    print(json.dumps(solve(), indent=2))
-          ^^^^
-NameError: name 'json' is not defined. Did you forget to import 'json'?</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Mother",
+      "Pet"
+    ],
+    "rows": [
+      [
+        "1",
+        "Bob",
+        "Penny",
+        "dog"
+      ],
+      [
+        "2",
+        "Peter",
+        "Sarah",
+        "fish"
+      ],
+      [
+        "3",
+        "Arnold",
+        "Janelle",
+        "cat"
+      ],
+      [
+        "4",
+        "Alice",
+        "Holly",
+        "bird"
+      ],
+      [
+        "5",
+        "Carol",
+        "Aniya",
+        "hamster"
+      ],
+      [
+        "6",
+        "Eric",
+        "Kailyn",
+        "rabbit"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x3-23</t>
+          <t>zebralogic_example_lgp-test-3x5-17</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "PhoneModel",
+      "Height",
+      "HouseStyle",
+      "CarModel"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "iphone 13",
+        "average",
+        "ranch",
+        "toyota camry"
+      ],
+      [
+        "2",
+        "Arnold",
+        "google pixel 6",
+        "short",
+        "colonial",
+        "ford f150"
+      ],
+      [
+        "3",
+        "Peter",
+        "samsung galaxy s21",
+        "very short",
+        "victorian",
+        "tesla model 3"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-3x3-23</t>
+          <t>zebralogic_example_lgp-test-2x3-23</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Children", "Food"], "rows": [["1", "Eric", "Bella", "grilled cheese"], ["2", "Arnold", "Fred", "pizza"]]}}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x3-8</t>
+          <t>zebralogic_example_lgp-test-3x3-23</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solution = solve_puzzle()
-               ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Occupation", "Hobby"], "rows": [["1", "Peter", "engineer", "gardening"], ["2", "Arnold", "doctor", "cooking"], ["3", "Eric", "teacher", "photography"]]}}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-4x2-26</t>
+          <t>zebralogic_example_lgp-test-2x3-8</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solution = solve_puzzle()
-               ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Birthday", "Mother"], "rows": [["1", "Eric", "april", "Aniya"], ["2", "Arnold", "sept", "Holly"]]}}</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-4x5-25</t>
+          <t>zebralogic_example_lgp-test-4x2-26</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve_puzzle()
-    ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Occupation"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "doctor"
+      ],
+      [
+        "2",
+        "Arnold",
+        "engineer"
+      ],
+      [
+        "3",
+        "Alice",
+        "artist"
+      ],
+      [
+        "4",
+        "Peter",
+        "teacher"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-4x3-38</t>
+          <t>zebralogic_example_lgp-test-4x5-25</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle", "HairColor", "Children", "BookGenre"], "rows": [["1", "Arnold", "victorian", "red", "Meredith", "science fiction"], ["2", "Eric", "ranch", "black", "Fred", "mystery"], ["3", "Peter", "craftsman", "blonde", "Bella", "fantasy"], ["4", "Alice", "colonial", "brown", "Samantha", "romance"]]}}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x3-31</t>
+          <t>zebralogic_example_lgp-test-4x3-38</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Mother", "Flower"], "rows": [["1", "Eric", "Aniya", "daffodils"], ["2", "Arnold", "Holly", "lilies"], ["3", "Alice", "Kailyn", "carnations"], ["4", "Peter", "Janelle", "roses"]]}}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x4-23</t>
+          <t>zebralogic_example_lgp-test-2x3-31</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "FavoriteSport", "Hobby"], "rows": [["1", "Arnold", "basketball", "gardening"], ["2", "Eric", "soccer", "photography"]]}}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-5x4-31</t>
+          <t>zebralogic_example_lgp-test-2x4-23</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Mother", "CarModel", "Height"], "rows": [["1", "Arnold", "Aniya", "ford f150", "short"], ["2", "Eric", "Holly", "tesla model 3", "very short"]]}}</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-3x5-0</t>
+          <t>zebralogic_example_lgp-test-5x4-31</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4047,169 +5079,236 @@
       <c r="G79" t="inlineStr">
         <is>
           <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 349, in &lt;module&gt;
+    solve()
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 321, in solve
+    backtrack(0)
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 306, in backtrack
+    backtrack(h + 1)
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 306, in backtrack
+    backtrack(h + 1)
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 306, in backtrack
+    backtrack(h + 1)
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-24 20:20:06.py", line 301, in backtrack
+    child_left.remove(ch)
+KeyError: 'Meredith'</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x4-4</t>
+          <t>zebralogic_example_lgp-test-3x5-0</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "BookGenre", "Smoothie", "Birthday", "Height"], "rows": [["1", "Eric", "science fiction", "watermelon", "april", "short"], ["2", "Arnold", "mystery", "desert", "sept", "average"], ["3", "Peter", "romance", "cherry", "jan", "very short"]]}}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x3-3</t>
+          <t>zebralogic_example_lgp-test-2x4-4</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle", "Height", "Education"], "rows": [["1", "Arnold", "victorian", "short", "associate"], ["2", "Eric", "colonial", "very short", "high school"]]}}</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-3x6-19</t>
+          <t>zebralogic_example_lgp-test-2x3-3</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve_puzzle()
-    ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Food", "Mother"], "rows": [["1", "Arnold", "grilled cheese", "Holly"], ["2", "Eric", "pizza", "Aniya"]]}}</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-4x5-21</t>
+          <t>zebralogic_example_lgp-test-3x6-19</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Cigar", "Animal", "Children", "BookGenre", "PhoneModel"], "rows": [["1", "Peter", "blue master", "bird", "Fred", "mystery", "google pixel 6"], ["2", "Arnold", "pall mall", "horse", "Meredith", "romance", "iphone 13"], ["3", "Eric", "prince", "cat", "Bella", "science fiction", "samsung galaxy s21"]]}}</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-4x5-21</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="b">
+        <v>0</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" t="b">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Smoothie",
+      "FavoriteSport",
+      "CarModel",
+      "Flower"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "cherry",
+        "tennis",
+        "tesla model 3",
+        "roses"
+      ],
+      [
+        "2",
+        "Alice",
+        "desert",
+        "soccer",
+        "toyota camry",
+        "carnations"
+      ],
+      [
+        "3",
+        "Arnold",
+        "watermelon",
+        "basketball",
+        "ford f150",
+        "lilies"
+      ],
+      [
+        "4",
+        "Peter",
+        "dragonfruit",
+        "swimming",
+        "honda civic",
+        "daffodils"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-6x6-29</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" t="b">
-        <v>0</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E84" t="b">
-        <v>0</v>
-      </c>
-      <c r="F84" t="b">
-        <v>0</v>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="b">
+        <v>0</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" t="b">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -4225,39 +5324,39 @@
     "rows": [
       [
         "1",
-        "Arnold",
+        "Carol",
         "colonial",
-        "stew",
+        "stir fry",
         "city",
-        "very short",
+        "average",
         "pall mall"
       ],
       [
         "2",
-        "Carol",
+        "Bob",
         "craftsman",
         "pizza",
         "cultural",
-        "very tall",
-        "blends"
+        "very short",
+        "prince"
       ],
       [
         "3",
         "Peter",
-        "ranch",
+        "modern",
         "grilled cheese",
         "camping",
+        "short",
+        "blends"
+      ],
+      [
+        "4",
+        "Eric",
+        "ranch",
+        "soup",
+        "beach",
         "tall",
         "blue master"
-      ],
-      [
-        "4",
-        "Eric",
-        "modern",
-        "stir fry",
-        "cruise",
-        "short",
-        "dunhill"
       ],
       [
         "5",
@@ -4265,331 +5364,123 @@
         "victorian",
         "spaghetti",
         "mountain",
-        "average",
+        "very tall",
         "yellow monster"
       ],
       [
         "6",
-        "Bob",
+        "Arnold",
         "mediterranean",
-        "soup",
-        "beach",
-        "super tal</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x2-32</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" t="b">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E85" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85" t="b">
-        <v>0</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+        "stew",
+        "cruise",
+        "super tall</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-5x5-9</t>
+          <t>zebralogic_example_lgp-test-2x2-32</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>1</v>
       </c>
       <c r="C86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    main()
-    ^^^^
-NameError: name 'main' is not defined. Did you mean: 'min'?</t>
+          <t>{"solution": {"header": ["House", "Name", "BookGenre"], "rows": [["1", "Eric", "science fiction"], ["2", "Arnold", "mystery"]]}}</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x5-9</t>
+          <t>zebralogic_example_lgp-test-5x5-9</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>1</v>
       </c>
       <c r="C87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="inlineStr">
-        <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x6-10</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" t="b">
-        <v>1</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E88" t="b">
-        <v>0</v>
-      </c>
-      <c r="F88" t="b">
-        <v>0</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x3-26</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" t="b">
-        <v>1</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E89" t="b">
-        <v>0</v>
-      </c>
-      <c r="F89" t="b">
-        <v>0</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x4-13</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" t="b">
-        <v>1</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E90" t="b">
-        <v>0</v>
-      </c>
-      <c r="F90" t="b">
-        <v>0</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solution = solve_puzzle()
-               ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x3-39</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" t="b">
-        <v>1</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E91" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91" t="b">
-        <v>0</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    solve()
-    ^^^^^
-NameError: name 'solve' is not defined</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x6-37</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" t="b">
-        <v>0</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E92" t="b">
-        <v>0</v>
-      </c>
-      <c r="F92" t="b">
-        <v>0</v>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Hobby",
-      "FavoriteSport",
-      "HouseStyle",
-      "Children",
-      "Height"
+      "Drink",
+      "Color",
+      "Flower",
+      "Hobby"
     ],
     "rows": [
       [
         "1",
+        "Eric",
+        "root beer",
+        "yellow",
+        "carnations",
+        "gardening"
+      ],
+      [
+        "2",
         "Arnold",
-        "knitting",
-        "swimming",
-        "craftsman",
-        "Meredith",
-        "average"
-      ],
-      [
-        "2",
+        "tea",
+        "white",
+        "roses",
+        "photography"
+      ],
+      [
+        "3",
+        "Peter",
+        "water",
+        "red",
+        "daffodils",
+        "knitting"
+      ],
+      [
+        "4",
+        "Bob",
+        "milk",
+        "blue",
+        "tulips",
+        "cooking"
+      ],
+      [
+        "5",
         "Alice",
-        "gardening",
-        "tennis",
-        "ranch",
-        "Timothy",
-        "tall"
-      ],
-      [
-        "3",
-        "Eric",
-        "cooking",
-        "basketball",
-        "modern",
-        "Samantha",
-        "short"
-      ],
-      [
-        "4",
-        "Peter",
-        "photography",
-        "baseball",
-        "colonial",
-        "Bella",
-        "very tall"
-      ],
-      [
-        "5",
-        "Bob",
-        "painting",
-        "soccer",
-        "victorian",
-        "Fred",
-        "very short"
+        "coffee",
+        "green",
+        "lilies",
+        "painting"
       ]
     ]
   }
@@ -4597,267 +5488,489 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x5-9</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="b">
+        <v>0</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E88" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" t="b">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "BookGenre", "Vacation", "Animal", "MusicGenre"], "rows": [["1", "Arnold", "mystery", "mountain", "cat", "rock"], ["2", "Eric", "science fiction", "beach", "horse", "pop"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x6-10</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="b">
+        <v>0</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E89" t="b">
+        <v>1</v>
+      </c>
+      <c r="F89" t="b">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Food", "Height", "Drink", "Pet", "PhoneModel"], "rows": [["1", "Arnold", "stir fry", "very tall", "milk", "dog", "oneplus 9"], ["2", "Carol", "soup", "average", "water", "bird", "samsung galaxy s21"], ["3", "Alice", "stew", "super tall", "boba tea", "fish", "iphone 13"], ["4", "Eric", "spaghetti", "very short", "tea", "rabbit", "google pixel 6"], ["5", "Peter", "pizza", "short", "root beer", "cat", "huawei p50"], ["6", "Bob", "grilled cheese", "tall", "coffee", "hamster", "xiaomi mi 11"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x3-26</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="b">
+        <v>0</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E90" t="b">
+        <v>1</v>
+      </c>
+      <c r="F90" t="b">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Height", "PhoneModel"], "rows": [["1", "Eric", "super tall", "huawei p50"], ["2", "Carol", "very tall", "xiaomi mi 11"], ["3", "Bob", "average", "samsung galaxy s21"], ["4", "Arnold", "tall", "google pixel 6"], ["5", "Peter", "very short", "oneplus 9"], ["6", "Alice", "short", "iphone 13"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x4-13</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="b">
+        <v>0</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E91" t="b">
+        <v>1</v>
+      </c>
+      <c r="F91" t="b">
+        <v>1</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Cigar", "FavoriteSport", "Drink"], "rows": [["1", "Alice", "prince", "soccer", "water"], ["2", "Arnold", "blue master", "tennis", "coffee"], ["3", "Eric", "dunhill", "basketball", "tea"], ["4", "Peter", "pall mall", "swimming", "milk"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x3-39</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="b">
+        <v>0</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E92" t="b">
+        <v>1</v>
+      </c>
+      <c r="F92" t="b">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "HairColor",
+      "FavoriteSport"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "brown",
+        "basketball"
+      ],
+      [
+        "2",
+        "Alice",
+        "red",
+        "swimming"
+      ],
+      [
+        "3",
+        "Peter",
+        "black",
+        "tennis"
+      ],
+      [
+        "4",
+        "Eric",
+        "blonde",
+        "soccer"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x2-14</t>
+          <t>zebralogic_example_lgp-test-5x6-37</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>1</v>
       </c>
       <c r="C93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Hobby", "FavoriteSport", "HouseStyle", "Children", "Height"], "rows": [["1", "Eric", "knitting", "swimming", "craftsman", "Meredith", "average"], ["2", "Alice", "gardening", "soccer", "ranch", "Timothy", "tall"], ["3", "Arnold", "cooking", "tennis", "modern", "Samantha", "very short"], ["4", "Peter", "photography", "baseball", "colonial", "Bella", "very tall"], ["5", "Bob", "painting", "basketball", "victorian", "Fred", "short"]]}}</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x3-32</t>
+          <t>zebralogic_example_lgp-test-2x2-14</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Food"], "rows": [["1", "Eric", "grilled cheese"], ["2", "Arnold", "pizza"]]}}</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x2-25</t>
+          <t>zebralogic_example_lgp-test-2x3-32</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>1</v>
       </c>
       <c r="C95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Birthday", "Color"], "rows": [["1", "Arnold", "april", "red"], ["2", "Eric", "sept", "yellow"]]}}</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-4x5-6</t>
+          <t>zebralogic_example_lgp-test-2x2-25</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>1</v>
       </c>
       <c r="C96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Vacation"], "rows": [["1", "Eric", "beach"], ["2", "Arnold", "mountain"]]}}</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-3x5-12</t>
+          <t>zebralogic_example_lgp-test-4x5-6</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    main()
-    ^^^^
-NameError: name 'main' is not defined. Did you mean: 'min'?</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Education",
+      "MusicGenre",
+      "Color",
+      "Flower"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "bachelor",
+        "jazz",
+        "yellow",
+        "daffodils"
+      ],
+      [
+        "2",
+        "Peter",
+        "associate",
+        "pop",
+        "green",
+        "roses"
+      ],
+      [
+        "3",
+        "Alice",
+        "master",
+        "rock",
+        "red",
+        "carnations"
+      ],
+      [
+        "4",
+        "Eric",
+        "high school",
+        "classical",
+        "white",
+        "lilies"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x6-1</t>
+          <t>zebralogic_example_lgp-test-3x5-12</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "Cigar", "Hobby", "Education", "Drink"], "rows": [["1", "Peter", "pall mall", "gardening", "bachelor", "water"], ["2", "Arnold", "blue master", "photography", "associate", "milk"], ["3", "Eric", "prince", "cooking", "high school", "tea"]]}}</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-4x4-21</t>
+          <t>zebralogic_example_lgp-test-2x6-1</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve_puzzle()
-             ^^^^^^^^^^^^
-NameError: name 'solve_puzzle' is not defined</t>
+          <t>{"solution": {"header": ["House", "Name", "FavoriteSport", "HairColor", "Height", "Smoothie", "Flower"], "rows": [["1", "Eric", "soccer", "black", "short", "desert", "carnations"], ["2", "Arnold", "basketball", "brown", "very short", "cherry", "daffodils"]]}}</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-4x4-21</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="b">
+        <v>0</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E100" t="b">
+        <v>1</v>
+      </c>
+      <c r="F100" t="b">
+        <v>1</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "CarModel", "Birthday", "Hobby"], "rows": [["1", "Alice", "honda civic", "sept", "photography"], ["2", "Arnold", "tesla model 3", "april", "painting"], ["3", "Eric", "ford f150", "feb", "cooking"], ["4", "Peter", "toyota camry", "jan", "gardening"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-5x4-7</t>
         </is>
       </c>
-      <c r="B100" t="n">
-        <v>1</v>
-      </c>
-      <c r="C100" t="b">
-        <v>1</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E100" t="b">
-        <v>0</v>
-      </c>
-      <c r="F100" t="b">
-        <v>0</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:34:08.py", line 2, in &lt;module&gt;
-    result = solve()
-             ^^^^^
-NameError: name 'solve' is not defined</t>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="b">
+        <v>0</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E101" t="b">
+        <v>1</v>
+      </c>
+      <c r="F101" t="b">
+        <v>1</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Smoothie", "Animal", "Nationality"], "rows": [["1", "Eric", "cherry", "cat", "swede"], ["2", "Peter", "desert", "dog", "german"], ["3", "Arnold", "lime", "horse", "dane"], ["4", "Alice", "dragonfruit", "fish", "norwegian"], ["5", "Bob", "watermelon", "bird", "brit"]]}}</t>
         </is>
       </c>
     </row>
